--- a/data/batches/B21_Mixed/Test_Validation_Report/Test_Validation_Report_B21.xlsx
+++ b/data/batches/B21_Mixed/Test_Validation_Report/Test_Validation_Report_B21.xlsx
@@ -582,56 +582,56 @@
         <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>FAIL - Missing in P21 Issue Summary</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
+          <t>Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11980,104 +11980,6 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B21_Mixed</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>usl261</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CT2003</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>FAIL - Missing in P21 Issue Summary</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -12242,56 +12144,56 @@
         <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>FAIL - Missing in P21 Issue Summary</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
+          <t>Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -12612,13 +12514,13 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -12630,7 +12532,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
     </row>
   </sheetData>
